--- a/artfynd/A 30593-2019 artfynd.xlsx
+++ b/artfynd/A 30593-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30593-2019 artfynd.xlsx
+++ b/artfynd/A 30593-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4778,327 +4778,6 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>112607079</v>
-      </c>
-      <c r="B37" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Hofors, Gstr</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>572375</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6714959</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Hofors</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Gästrikland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Torsåker</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>112607053</v>
-      </c>
-      <c r="B38" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Hofors, Gstr</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>572374</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6714966</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Hofors</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Gästrikland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Torsåker</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>112607076</v>
-      </c>
-      <c r="B39" t="n">
-        <v>96996</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Hofors, Gstr</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>572301</v>
-      </c>
-      <c r="R39" t="n">
-        <v>6714848</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Hofors</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Gästrikland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Torsåker</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2022-09-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
